--- a/artfynd/A 30308-2023 artfynd.xlsx
+++ b/artfynd/A 30308-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126838098</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126838074</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>126838073</v>
       </c>
       <c r="B5" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>126838099</v>
       </c>
       <c r="B6" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>126838097</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>126838175</v>
       </c>
       <c r="B8" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
